--- a/Exp3_PTO_GRPO/eda/results/arms/outcomes/tables/claude-haiku-4-5/headline/headline.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/outcomes/tables/claude-haiku-4-5/headline/headline.xlsx
@@ -630,37 +630,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.798</v>
+        <v>2.903</v>
       </c>
       <c r="E5" t="n">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="F5" t="n">
-        <v>2.736</v>
+        <v>2.875</v>
       </c>
       <c r="G5" t="n">
-        <v>3.097</v>
+        <v>3.233</v>
       </c>
       <c r="H5" t="n">
-        <v>2.185</v>
+        <v>2.344</v>
       </c>
       <c r="I5" t="n">
-        <v>0.622</v>
+        <v>0.677</v>
       </c>
       <c r="J5" t="n">
-        <v>0.647</v>
+        <v>0.575</v>
       </c>
       <c r="K5" t="n">
-        <v>0.623</v>
+        <v>0.788</v>
       </c>
       <c r="L5" t="n">
-        <v>0.63</v>
+        <v>0.527</v>
       </c>
       <c r="M5" t="n">
-        <v>0.206</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="6">
@@ -810,37 +810,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>2.798</v>
+        <v>2.903</v>
       </c>
       <c r="E9" t="n">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="F9" t="n">
-        <v>2.736</v>
+        <v>2.875</v>
       </c>
       <c r="G9" t="n">
-        <v>3.097</v>
+        <v>3.233</v>
       </c>
       <c r="H9" t="n">
-        <v>2.185</v>
+        <v>2.344</v>
       </c>
       <c r="I9" t="n">
-        <v>0.622</v>
+        <v>0.677</v>
       </c>
       <c r="J9" t="n">
-        <v>0.647</v>
+        <v>0.575</v>
       </c>
       <c r="K9" t="n">
-        <v>0.623</v>
+        <v>0.788</v>
       </c>
       <c r="L9" t="n">
-        <v>0.63</v>
+        <v>0.527</v>
       </c>
       <c r="M9" t="n">
-        <v>0.206</v>
+        <v>0.289</v>
       </c>
     </row>
   </sheetData>

--- a/Exp3_PTO_GRPO/eda/results/arms/outcomes/tables/claude-haiku-4-5/headline/headline.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/outcomes/tables/claude-haiku-4-5/headline/headline.xlsx
@@ -630,37 +630,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>2.903</v>
+        <v>2.873</v>
       </c>
       <c r="E5" t="n">
-        <v>2.96</v>
+        <v>2.957</v>
       </c>
       <c r="F5" t="n">
-        <v>2.875</v>
+        <v>2.935</v>
       </c>
       <c r="G5" t="n">
-        <v>3.233</v>
+        <v>3.328</v>
       </c>
       <c r="H5" t="n">
-        <v>2.344</v>
+        <v>2.375</v>
       </c>
       <c r="I5" t="n">
-        <v>0.677</v>
+        <v>0.725</v>
       </c>
       <c r="J5" t="n">
-        <v>0.575</v>
+        <v>0.628</v>
       </c>
       <c r="K5" t="n">
-        <v>0.788</v>
+        <v>1.56</v>
       </c>
       <c r="L5" t="n">
-        <v>0.527</v>
+        <v>0.658</v>
       </c>
       <c r="M5" t="n">
-        <v>0.289</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="6">
@@ -810,37 +810,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>2.903</v>
+        <v>2.912</v>
       </c>
       <c r="E9" t="n">
-        <v>2.96</v>
+        <v>2.888</v>
       </c>
       <c r="F9" t="n">
-        <v>2.875</v>
+        <v>2.792</v>
       </c>
       <c r="G9" t="n">
-        <v>3.233</v>
+        <v>3.205</v>
       </c>
       <c r="H9" t="n">
-        <v>2.344</v>
+        <v>2.383</v>
       </c>
       <c r="I9" t="n">
-        <v>0.677</v>
+        <v>0.668</v>
       </c>
       <c r="J9" t="n">
-        <v>0.575</v>
+        <v>0.58</v>
       </c>
       <c r="K9" t="n">
-        <v>0.788</v>
+        <v>0.929</v>
       </c>
       <c r="L9" t="n">
-        <v>0.527</v>
+        <v>0.616</v>
       </c>
       <c r="M9" t="n">
-        <v>0.289</v>
+        <v>0.335</v>
       </c>
     </row>
   </sheetData>
